--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_852_USA_Gulf_of_Mexico.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_852_USA_Gulf_of_Mexico.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb23a84a4187846d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1f6cbd8fc8664042"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R90c58d7cd91e4ca4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R83a16e4b1dc34b7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R0015d9d75bea42cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re6fe931ca61c48d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re61e3db906eb4329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8e9f44cb551f4531"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc1e6da6374b94712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra1a9214b6429449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R0e0a2ebf034d4e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb94c0cc19db24b50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ852CommercialTable" displayName="EEZ852CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ852CommercialTable" displayName="EEZ852CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ852FunctionalTable" displayName="EEZ852FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ852FunctionalTable" displayName="EEZ852FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ852ValidationTable" displayName="EEZ852ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ852ValidationTable" displayName="EEZ852ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -25819,7 +25773,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12233f25c768492e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R035390401a9249f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25829,20 +25783,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -25850,660 +25794,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>68.2644818689</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.34</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>218.77616239495518</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>68.2644818689</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$376,A2,'Species'!$U$2:$U$376))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>14934.64137115794</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.34</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>14934.64137115794</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5.0458315365</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9099999999999997</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>812.8305161640986</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5.0458315365</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$376,A3,'Species'!$U$2:$U$376))</x:f>
-        <x:v>4101.405852290386</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9099999999999997</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>812.8305161640986</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4101.4058522903815</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>4.547473508864641e-12</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.1087596967086685e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>140760.2274834424</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.0938490930970803</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>124.12209381832832</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>140760.2274834424</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>248.044909123369</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$376,A4,'Species'!$U$2:$U$376))</x:f>
-        <x:v>34914857.83431522</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.0938490930970803</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>124.12209381832832</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>17471454.161589075</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>17443403.672726143</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.9983944960388815</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.9983944960388815</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>369.8143464417</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.765620835283373</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>582.9359445558626</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>369.8143464417</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>584.0855083911059</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$376,A5,'Species'!$U$2:$U$376))</x:f>
-        <x:v>216003.20055172493</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.765620835283373</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>582.9359445558626</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>215578.07535330142</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>425.1251984235132</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0019720242781034</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0019720242781033934</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>639414.9387617346</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.945156446439089</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>88.13663115069147</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>639414.9387617346</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>127.92684980177546</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$376,A6,'Species'!$U$2:$U$376))</x:f>
-        <x:v>81798338.83198388</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.945156446439089</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>88.13663115069147</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>56355878.60988498</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>25442460.222098902</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.451460625753357</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.45146062575335705</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>27370.1976902875</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0436588095781283</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.057547396374295</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>27370.1976902875</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>14.157560607932469</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$376,A7,'Species'!$U$2:$U$376))</x:f>
-        <x:v>387495.23265133856</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0436588095781283</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.057547396374295</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>302647.2582084883</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>84847.97444285027</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2803526949000146</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2803526949000147</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>131615.8841629343</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.16753987944954</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>147.07534623556302</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>131615.8841629343</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>178.71481810909253</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$376,A8,'Species'!$U$2:$U$376))</x:f>
-        <x:v>23521708.798446193</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.16753987944954</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>147.07534623556302</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>19357451.733363315</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>4164257.065082878</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2151242385848557</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.21512423858485566</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>159577.92729074782</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6995708606302453</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>500.69224012761987</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>159577.92729074782</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>853.3491282726085</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$376,A9,'Species'!$U$2:$U$376))</x:f>
-        <x:v>136175685.14510936</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6995708606302453</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>500.69224012761987</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>79899429.89012697</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>56276255.25498238</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.704338633359089</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.7043386333590891</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>65.85848659399998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.871241526308358</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>743.432471677719</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>65.85848659399998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>797.9932526561673</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$376,A10,'Species'!$U$2:$U$376))</x:f>
-        <x:v>52554.62793215864</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.871241526308358</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>743.432471677719</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>48961.33746953133</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3593.2904626273084</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0733903657117907</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.07339036571179076</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1864.7764262068</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.122694285282179</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1326.4603882380961</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1864.7764262068</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1553.813497700655</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$376,A11,'Species'!$U$2:$U$376))</x:f>
-        <x:v>2897514.7812341154</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.122694285282179</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1326.4603882380961</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2473552.062283521</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>423962.7189505943</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1713983406353705</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.17139834063537057</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3081.0915413233997</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.454946091590354</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2850.664396274679</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3081.0915413233997</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2871.2247108546117</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$376,A12,'Species'!$U$2:$U$376))</x:f>
-        <x:v>8846506.169852868</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.454946091590354</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2850.664396274679</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>8783157.958513688</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>63348.21133917943</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0072124640861975</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.007212464086197466</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69dcefcc2c914667"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f9f620bc35644e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26513,20 +26028,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -26534,1362 +26039,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>31.433898917899995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.010714097880878</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1024.9769474711247</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>31.433898917899995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1189.96553122335</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$376,A2,'Species'!$U$2:$U$376))</x:f>
-        <x:v>37405.25622425995</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.010714097880878</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1024.9769474711247</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>32219.02175998503</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5186.234464274923</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1609680921695784</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.16096809216957841</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1178.0768345238</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3479529788450884</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>222.81938891888055</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1178.0768345238</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>223.3906787445944</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$376,A3,'Species'!$U$2:$U$376))</x:f>
-        <x:v>263171.3836775549</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3479529788450884</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>222.81938891888055</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>262498.3603680823</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>673.0233094725991</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0025639143365652</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0025639143365652553</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>11.3055527975</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.670657186036108</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>468.4434664174058</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>11.3055527975</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>470.1430122981119</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$376,A4,'Species'!$U$2:$U$376))</x:f>
-        <x:v>5315.226647911996</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.670657186036108</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>468.4434664174058</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>5296.012342225899</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>19.21430568609685</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0036280704130724</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0036280704130725516</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>10.600012700099999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>10.600012700099999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$376,A5,'Species'!$U$2:$U$376))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>23190.300998656647</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>23190.300998656647</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4802.5151519273</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.328799888091536</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>21.320622864244168</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4802.5151519273</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>171.969819306688</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$376,A6,'Species'!$U$2:$U$376))</x:f>
-        <x:v>825887.6628945692</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.328799888091536</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>21.320622864244168</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>102392.61435406025</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>723495.048540509</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>8.065890963959157</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>7.0658909639591565</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>28576.661550870205</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.98795116464373</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>972.6378468715862</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>28576.661550870205</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1008.0918275582702</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$376,A7,'Species'!$U$2:$U$376))</x:f>
-        <x:v>28807898.968330897</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.98795116464373</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>972.6378468715862</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>27794742.56161644</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1013156.406714458</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.036451368616509</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0364513686165092</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>15243.902842790398</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.373855055931779</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2365.1302128812167</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>15243.902842790398</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2446.4112613634493</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$376,A8,'Species'!$U$2:$U$376))</x:f>
-        <x:v>37292855.58173273</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.373855055931779</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2365.1302128812167</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>36053815.17570944</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1239040.4060232863</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.034366415869854</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.03436641586985407</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>198.6090022055</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.582847559668311</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>382.69039279554454</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>198.6090022055</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>458.5682392361029</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$376,A9,'Species'!$U$2:$U$376))</x:f>
-        <x:v>91075.78043781541</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.582847559668311</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>382.69039279554454</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>76005.75706675397</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>15070.023371061441</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1982747617108243</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.19827476171082428</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>8295.2461044627</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.642385895352341</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>438.92053041469853</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>8295.2461044627</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>701.7855040832553</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$376,A10,'Species'!$U$2:$U$376))</x:f>
-        <x:v>5821483.468915015</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.642385895352341</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>438.92053041469853</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3640953.82009123</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2180529.6488237856</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.598889674675728</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.598889674675728</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1660.4118553537999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.189218524084256</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1546.0321613234275</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1660.4118553537999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1688.9482922135003</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$376,A11,'Species'!$U$2:$U$376))</x:f>
-        <x:v>2804349.7674708497</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.189218524084256</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1546.0321613234275</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2567050.1294196774</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>237299.63805117225</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0924405937116692</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.09244059371166921</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>30947.654859430007</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.8677924180071623</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>737.5516144829209</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>30947.654859430007</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>841.7474187853994</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$376,A12,'Species'!$U$2:$U$376))</x:f>
-        <x:v>26050108.59538663</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.8677924180071623</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>737.5516144829209</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>22825492.806032814</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>3224615.7893538177</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1412725594472837</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.14127255944728373</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>45.774857692400005</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.976160259110686</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>946.5863969989255</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>45.774857692400005</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1141.9281500794552</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$376,A13,'Species'!$U$2:$U$376))</x:f>
-        <x:v>52271.59856483266</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.976160259110686</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>946.5863969989255</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>43329.857616187466</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>8941.740948645194</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.20636442029998</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.20636442029997987</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>15209.6099465302</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.3226648839614543</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>210.21557206403804</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>15209.6099465302</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>261.7844352652716</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$376,A14,'Species'!$U$2:$U$376))</x:f>
-        <x:v>3981639.1504574665</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.3226648839614543</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>210.21557206403804</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3197296.855780729</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>784342.2946767374</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2453141919739616</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.24531419197396154</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>176333.895523458</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3696643801369794</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>234.2417910830551</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>176333.895523458</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>341.00139763777617</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$376,A15,'Species'!$U$2:$U$376))</x:f>
-        <x:v>60130104.82441278</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3696643801369794</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>234.2417910830551</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>41304767.51606711</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>18825337.308345668</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4557666933005449</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.45576669330054487</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>148949.9341605235</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.2271180927270393</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>16.8701169280401</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>148949.9341605235</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>44.60927097127409</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$376,A16,'Species'!$U$2:$U$376))</x:f>
-        <x:v>6644547.974120228</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.2271180927270393</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>16.8701169280401</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2512802.805711906</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4131745.1684083217</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.6442775211076506</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.6442775211076504</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>24677.895787067697</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.8964535394257545</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>787.8681412614972</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>24677.895787067697</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1027.944854136818</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$376,A17,'Species'!$U$2:$U$376))</x:f>
-        <x:v>25367515.985240903</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.8964535394257545</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>787.8681412614972</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>19442927.88400196</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>5924588.101238944</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.3047168686005268</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.3047168686005268</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>42679.722489916996</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.17188549234632</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>14.855439067672984</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>42679.722489916996</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>18.330482029203246</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$376,A18,'Species'!$U$2:$U$376))</x:f>
-        <x:v>782339.8861128051</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.17188549234632</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>14.855439067672984</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>634026.0168741542</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>148313.8692386509</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2339239483733824</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.23392394837338235</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>109812.5726240124</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.8757344425817397</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>75.1163440740015</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>109812.5726240124</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>80.72617758697474</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$376,A19,'Species'!$U$2:$U$376))</x:f>
-        <x:v>8864749.238928586</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.8757344425817397</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>75.1163440740015</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>8248718.988876594</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>616030.250051992</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.074681929507201</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.07468192950720098</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>759.7447929847999</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.363809721481767</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>231.10520213757323</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>759.7447929847999</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>349.0647289300924</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$376,A20,'Species'!$U$2:$U$376))</x:f>
-        <x:v>265200.1102192883</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.363809721481767</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>231.10520213757323</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>175580.97395572093</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>89619.1362635674</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.510414848741915</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.5104148487419149</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>295.3572051056</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>4.217639873363484</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>1650.5925225867077</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>295.3572051056</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>2456.399242580576</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$376,A21,'Species'!$U$2:$U$376))</x:f>
-        <x:v>725515.2149121116</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>4.217639873363484</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>1650.5925225867077</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>487514.39423941186</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>238000.82067269977</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.4881923969527364</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.48819239695273636</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>493982.1027114975</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.16741766410722</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>147.033963405228</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>493982.1027114975</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>161.04766609503352</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$376,A22,'Species'!$U$2:$U$376))</x:f>
-        <x:v>79554664.7344038</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.16741766410722</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>147.033963405228</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>72632146.41291991</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>6922518.321483895</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0953092902160537</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.0953092902160538</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>115.42882326040001</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>4.175710661091475</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>1498.686037037652</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>115.42882326040001</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>1908.687268138038</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$376,A23,'Species'!$U$2:$U$376))</x:f>
-        <x:v>220317.52533328132</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>4.175710661091475</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>1498.686037037652</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>172991.56569204843</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>47325.95964123288</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.2735737979589152</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.2735737979589153</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>369.8143464417</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.765620835283373</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>582.9359445558626</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>369.8143464417</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>584.0855083911059</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$376,A24,'Species'!$U$2:$U$376))</x:f>
-        <x:v>216003.20055172493</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.765620835283373</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>582.9359445558626</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>215578.07535330142</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>425.1251984235132</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0019720242781034</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.0019720242781033934</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>5.7555686475000005</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.559897547780399</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>362.9924129604994</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>5.7555686475000005</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>362.993381437254</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$376,A25,'Species'!$U$2:$U$376))</x:f>
-        <x:v>2089.233325450268</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.559897547780399</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>362.9924129604994</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>2089.2277513158233</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0.005574134444486845</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0000026680358045</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.0000026680358046058793</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07611f8a082c4eb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R808ef303aa1c4553"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28064,7 +26685,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -28163,7 +26784,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>288829700.6693001</x:v>
+        <x:v>184927147.1340163</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28177,7 +26798,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>288829700.6693002</x:v>
+        <x:v>242453427.13459975</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28191,7 +26812,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-103902553.5352839</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28205,7 +26826,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-46376273.53470045</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -28216,9 +26837,9 @@
         <x:v>EEZ_852</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -28230,47 +26851,19 @@
         <x:v>EEZ_852</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_852</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_852</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97b5a05c01ff4e15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d87336a89b64f71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28317,7 +26910,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
